--- a/Proposal Web App/data/TNSE_Projects.xlsx
+++ b/Proposal Web App/data/TNSE_Projects.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="152">
   <si>
     <t>lead_id</t>
   </si>
@@ -79,6 +79,150 @@
     <t>updated</t>
   </si>
   <si>
+    <t>L261027-01</t>
+  </si>
+  <si>
+    <t>2026-07-15</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>New coastal house, Sullivan's Island - intro from Marisol Tran</t>
+  </si>
+  <si>
+    <t>2618 Atlantic Ave</t>
+  </si>
+  <si>
+    <t>Attachments: SDS_Atlantic_CD50_2026-07-14.pdf (22.4 MB), Atlantic_survey_2026-05.pdf (2.2 MB) Marisol Tran over at Palmetto Line gave me your name. She says you are the person to call for piles and high wind, and that you do not make her cry at permit time. I'm Owen Pruitt, I run Saltmarsh Design Studio, a one-man shop in Mount Pleasant, mostly coastal residential. We have not worked together before. The project is a new house at 2618 Atlantic Ave, Sullivan's Island. VE zone, BFE 14, and the Town wants two feet of freeboard on top of that. About 3,400 SF, two stories, wood framed, sitting on timber piles with grade beams and pile caps. The ground level is breakaway walls and parking.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From: Owen Pruitt &lt;owen@saltmarshdesign.example&gt;
+To: engineer@examplestructural.example
+Date: Wed, 15 Jul 2026 12:03:40 -0400
+Subject: New coastal house, Sullivan's Island - intro from Marisol Tran
+Attachments: SDS_Atlantic_CD50_2026-07-14.pdf (22.4 MB), Atlantic_survey_2026-05.pdf (2.2 MB)
+Hello,
+Marisol Tran over at Palmetto Line gave me your name. She says you are the person to call for piles and high wind, and that you do not make her cry at permit time. I'm Owen Pruitt, I run Saltmarsh Design Studio, a one-man shop in Mount Pleasant, mostly coastal residential. We have not worked together before.
+The project is a new house at 2618 Atlantic Ave, Sullivan's Island. VE zone, BFE 14, and the Town wants two feet of freeboard on top of that. About 3,400 SF, two stories, wood framed, sitting on timber piles with grade beams and pile caps. The ground level is breakaway walls and parking. I designed to 155 mph Exposure D. CDs are at 50% (attached, along with the survey).
+Where things stand:
+- The geotech is not back yet. The driller says next week and I'll send it the day I have it.
+- The owners want to submit to the Town in September and I'd like an engineer on board before then
+- I'd like one fee that covers the foundation, the framing, the shear walls, and the uplift connections, plus site visits during construction
+The owners are cost sensitive, so lump sum is strongly preferred. I'm the owner of the firm and also the billing contact, so everything can come straight to me.
+Owen
+Owen Pruitt, Owner / Architect
+Saltmarsh Design Studio
+1480 Ben Sawyer Blvd, Suite B, Mount Pleasant SC 29464
+843-555-0162</t>
+  </si>
+  <si>
+    <t>Bid - Preparing Proposal</t>
+  </si>
+  <si>
+    <t>Bid</t>
+  </si>
+  <si>
+    <t>Auto-bid from email intake (review)</t>
+  </si>
+  <si>
+    <t>C0001</t>
+  </si>
+  <si>
+    <t>26001</t>
+  </si>
+  <si>
+    <t>2026-10-27 22:27:31</t>
+  </si>
+  <si>
+    <t>L261027-02</t>
+  </si>
+  <si>
+    <t>2026-09-03</t>
+  </si>
+  <si>
+    <t>Structural sub needed - NS Norfolk CEP-204 chiller platform (design-build)</t>
+  </si>
+  <si>
+    <t>Naval Station Norfolk</t>
+  </si>
+  <si>
+    <t>VA</t>
+  </si>
+  <si>
+    <t>Attachments: MFB_CEP204_RFP_excerpts.pdf (3.4 MB) Pete Lindqvist gave me your name. We used to work together and he says you are licensed in Virginia and have done Navy work. I'm the program manager at Meridian Federal Builders. We are the design-build prime on a chiller replacement at the central energy plant, Building CEP-204, Naval Station Norfolk, VA 23511. We have not worked together before. We need a structural engineer to design an exterior elevated steel platform to carry the two new chillers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From: Dana Reyes &lt;dreyes@meridianfed.example&gt;
+To: engineer@examplestructural.example
+Date: Thu, 3 Sep 2026 08:40:11 -0400
+Subject: Structural sub needed - NS Norfolk CEP-204 chiller platform (design-build)
+Attachments: MFB_CEP204_RFP_excerpts.pdf (3.4 MB)
+Hello,
+Pete Lindqvist gave me your name. We used to work together and he says you are licensed in Virginia and have done Navy work. I'm the program manager at Meridian Federal Builders. We are the design-build prime on a chiller replacement at the central energy plant, Building CEP-204, Naval Station Norfolk, VA 23511. We have not worked together before.
+We need a structural engineer to design an exterior elevated steel platform to carry the two new chillers. The scope as I understand it:
+- Platform about 24 ft x 40 ft with 14 ft of clear height underneath
+- Drilled pier foundations
+- Braced frame lateral system
+- Grating with removable panels for equipment access
+- Evaluation of the existing maintenance crane rail that the new equipment will sit near
+- Antiterrorism standoff review per UFC 4-010-01
+The contract requires submittals at 65% and 100% through DrChecks, a UFC compliance narrative, and a design analysis. All drawings must be sealed by a Virginia PE. You would be our subcontractor, not the Navy's.
+I've attached the relevant RFP excerpts. The 65% submittal is due October 30. Before I send a subcontract I need:
+- Your Virginia license number
+- Your professional liability limits
+- A lump sum price covering design through 100% and our responses to the review comments
+Dana Reyes
+Program Manager, Meridian Federal Builders Inc.
+5800 Thurston Ave, Bldg 4, Virginia Beach VA 23455
+757-555-0150</t>
+  </si>
+  <si>
+    <t>2026-10-30</t>
+  </si>
+  <si>
+    <t>New</t>
+  </si>
+  <si>
+    <t>2026-10-27 23:02:10</t>
+  </si>
+  <si>
+    <t>L261027-03</t>
+  </si>
+  <si>
+    <t>2026-07-20</t>
+  </si>
+  <si>
+    <t>Atlantic Ave - geotech is in, and one change to what I asked for</t>
+  </si>
+  <si>
+    <t>Attachments: Atlantic_geotech_2026-06.pdf (9.5 MB) Geotech finally came in, attached. Their recommendation is driven timber piles and the report has the capacities. They also want pile driving records kept for every pile. The change: I called the Town this morning and the building official says the pile driving has to be observed by the engineer of record. So please add to the proposal: - Pile driving criteria in the drawings, based on the geotech - Your inspection when the piles are driven That makes three site visits for the project: piles, framing, and a final. If that changes the number, tell me and I will explain it to the owners.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From: Owen Pruitt &lt;owen@saltmarshdesign.example&gt;
+To: engineer@examplestructural.example
+Date: Mon, 20 Jul 2026 17:26:03 -0400
+Subject: RE: Atlantic Ave - geotech is in, and one change to what I asked for
+Attachments: Atlantic_geotech_2026-06.pdf (9.5 MB)
+Geotech finally came in, attached. Their recommendation is driven timber piles and the report has the capacities. They also want pile driving records kept for every pile.
+The change: I called the Town this morning and the building official says the pile driving has to be observed by the engineer of record. So please add to the proposal:
+- Pile driving criteria in the drawings, based on the geotech
+- Your inspection when the piles are driven
+That makes three site visits for the project: piles, framing, and a final. If that changes the number, tell me and I will explain it to the owners. I'd rather hear a bigger number now than a surprise later.
+Timing matters on this one. The owners' construction loan closes in October and the lender wants the permit application filed by September 14, so I need the revised proposal this week.
+One other thing. The Town confirmed the design flood elevation is 16 ft (BFE 14 plus the two feet of freeboard), and my CDs still show the lowest floor a foot under that. I'm fixing the floor elevations and will send the update this week.
+Owen</t>
+  </si>
+  <si>
+    <t>2026-09-14</t>
+  </si>
+  <si>
+    <t>26002</t>
+  </si>
+  <si>
+    <t>2026-10-27 23:04:27</t>
+  </si>
+  <si>
     <t>title</t>
   </si>
   <si>
@@ -106,6 +250,36 @@
     <t>created</t>
   </si>
   <si>
+    <t>Saltmarsh Design Studio</t>
+  </si>
+  <si>
+    <t>Owen Pruitt</t>
+  </si>
+  <si>
+    <t>843-555-0162</t>
+  </si>
+  <si>
+    <t>owen@saltmarshdesign.example</t>
+  </si>
+  <si>
+    <t>1480 Ben Sawyer Blvd</t>
+  </si>
+  <si>
+    <t>Mount Pleasant</t>
+  </si>
+  <si>
+    <t>SC</t>
+  </si>
+  <si>
+    <t>29464</t>
+  </si>
+  <si>
+    <t>Owner</t>
+  </si>
+  <si>
+    <t>2026-10-27</t>
+  </si>
+  <si>
     <t>name</t>
   </si>
   <si>
@@ -154,6 +328,52 @@
     <t>proposal_path</t>
   </si>
   <si>
+    <t>FL</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>Standard</t>
+  </si>
+  <si>
+    <t>Proposal</t>
+  </si>
+  <si>
+    <t>C:\Users\Seth Roswurm\Documents\GitHub\SE_Manager\Proposal Web App\data\Projects\26001 - New coastal house, Sullivan's Island - intro from Marisol Tran</t>
+  </si>
+  <si>
+    <t>The project is a new house at 2618 Atlantic Ave, Sullivan's Island. VE zone, BFE 14, and the Town wants two feet of freeboard on top of that. About 3,400 SF, two stories, wood framed, sitting on timber piles with grade beams and pile caps. The ground level is breakaway walls and parking.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Architectural drawings and a geotechnical report (where required) will be furnished by the client.
+Design will be in accordance with the governing edition of the Florida Building Code and referenced standards, unless otherwise noted.
+One round of minor revisions in response to building department comments is included.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Civil, MEP, architectural, and geotechnical engineering.
+Delegated design of components by others (e.g., trusses, pre-engineered metal building systems), unless listed in the scope.
+Changes in scope after a milestone has been issued; these will be billed as additional services.</t>
+  </si>
+  <si>
+    <t>{"options":{"methods":{}},"base":3000,"methods":[{"key":"hourly","fee":3000,"enabled":true},{"key":"area","fee":5950,"enabled":false},{"key":"dms","fee":0,"enabled":false},{"key":"historic","fee":0,"enabled":false}]}</t>
+  </si>
+  <si>
+    <t>C:\Users\Seth Roswurm\Documents\GitHub\SE_Manager\Proposal Web App\data\proposals\26001 - TNSE Proposal R0.pdf</t>
+  </si>
+  <si>
+    <t>2026-10-27 22:28:40</t>
+  </si>
+  <si>
+    <t>Expedited</t>
+  </si>
+  <si>
+    <t>C:\Users\Seth Roswurm\Documents\GitHub\SE_Manager\Proposal Web App\data\Projects\26002 - Atlantic Ave - geotech is in, and one change to what I asked for</t>
+  </si>
+  <si>
+    <t>{"options":{"methods":{}},"base":0,"methods":[{"key":"hourly","fee":0,"enabled":false},{"key":"area","fee":0,"enabled":false},{"key":"dms","fee":0,"enabled":false},{"key":"historic","fee":0,"enabled":false}]}</t>
+  </si>
+  <si>
     <t>line</t>
   </si>
   <si>
@@ -187,6 +407,18 @@
     <t>fee</t>
   </si>
   <si>
+    <t>Structural Drawings</t>
+  </si>
+  <si>
+    <t>design</t>
+  </si>
+  <si>
+    <t>hourly</t>
+  </si>
+  <si>
+    <t>engineering</t>
+  </si>
+  <si>
     <t>milestone</t>
   </si>
   <si>
@@ -202,6 +434,9 @@
     <t>note</t>
   </si>
   <si>
+    <t>2026-11-30</t>
+  </si>
+  <si>
     <t>year</t>
   </si>
   <si>
@@ -215,6 +450,84 @@
   </si>
   <si>
     <t>detail</t>
+  </si>
+  <si>
+    <t>2026-10-27 22:25:55</t>
+  </si>
+  <si>
+    <t>intake_rfp</t>
+  </si>
+  <si>
+    <t>email: New coastal house, Sullivan's Island - intro from Marisol Tran</t>
+  </si>
+  <si>
+    <t>decide_bid</t>
+  </si>
+  <si>
+    <t>Bid (100%) Auto-bid from email intake (review)</t>
+  </si>
+  <si>
+    <t>create_client</t>
+  </si>
+  <si>
+    <t>create_project</t>
+  </si>
+  <si>
+    <t>generate_folders</t>
+  </si>
+  <si>
+    <t>script for 32 folder(s): 01_Correspondence, 02_Contract &amp; Proposal, 03_Client Documents, 04_Design, 05_Revit, 07_Issued Drawings, 08_Submittals, 10_Inspections, 11_Reports &amp; Letters, 12_Invoices</t>
+  </si>
+  <si>
+    <t>set_scope</t>
+  </si>
+  <si>
+    <t>1 line(s)</t>
+  </si>
+  <si>
+    <t>estimate_fee</t>
+  </si>
+  <si>
+    <t>total 3750</t>
+  </si>
+  <si>
+    <t>set_milestones</t>
+  </si>
+  <si>
+    <t>100%@2026-11-30</t>
+  </si>
+  <si>
+    <t>generate_proposal</t>
+  </si>
+  <si>
+    <t>R0 C:\Users\Seth Roswurm\Documents\GitHub\SE_Manager\Proposal Web App\data\proposals\26001 - TNSE Proposal R0.pdf</t>
+  </si>
+  <si>
+    <t>2026-10-27 22:26:43</t>
+  </si>
+  <si>
+    <t>Bid (86%) Auto-bid from email intake (review)</t>
+  </si>
+  <si>
+    <t>update_client</t>
+  </si>
+  <si>
+    <t>2026-10-27 22:28:37</t>
+  </si>
+  <si>
+    <t>update_project</t>
+  </si>
+  <si>
+    <t>name, address, state, project_type, sf, expedite, description</t>
+  </si>
+  <si>
+    <t>email: Structural sub needed - NS Norfolk CEP-204 chiller platform (design-build)</t>
+  </si>
+  <si>
+    <t>email: Atlantic Ave - geotech is in, and one change to what I asked for</t>
+  </si>
+  <si>
+    <t>total 0</t>
   </si>
 </sst>
 </file>
@@ -601,7 +914,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T1"/>
+  <dimension ref="A1:T4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="12" customWidth="1"/>
@@ -680,6 +993,192 @@
         <v>19</v>
       </c>
     </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P2" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q2">
+        <v>86</v>
+      </c>
+      <c r="R2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S2" t="s">
+        <v>31</v>
+      </c>
+      <c r="T2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M3" t="s">
+        <v>40</v>
+      </c>
+      <c r="N3" t="s">
+        <v>41</v>
+      </c>
+      <c r="O3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>22</v>
+      </c>
+      <c r="R3" t="s">
+        <v>22</v>
+      </c>
+      <c r="S3" t="s">
+        <v>22</v>
+      </c>
+      <c r="T3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" t="s">
+        <v>45</v>
+      </c>
+      <c r="I4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" t="s">
+        <v>46</v>
+      </c>
+      <c r="L4" t="s">
+        <v>47</v>
+      </c>
+      <c r="M4" t="s">
+        <v>48</v>
+      </c>
+      <c r="N4" t="s">
+        <v>27</v>
+      </c>
+      <c r="O4" t="s">
+        <v>28</v>
+      </c>
+      <c r="P4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q4">
+        <v>100</v>
+      </c>
+      <c r="R4" t="s">
+        <v>30</v>
+      </c>
+      <c r="S4" t="s">
+        <v>49</v>
+      </c>
+      <c r="T4" t="s">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:T1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -689,7 +1188,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -713,7 +1212,7 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
@@ -722,31 +1221,78 @@
         <v>6</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>28</v>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I2" t="s">
+        <v>66</v>
+      </c>
+      <c r="J2" t="s">
+        <v>67</v>
+      </c>
+      <c r="K2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s">
+        <v>68</v>
+      </c>
+      <c r="N2" t="s">
+        <v>22</v>
+      </c>
+      <c r="O2" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -758,7 +1304,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z1"/>
+  <dimension ref="A1:Z3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -791,73 +1337,233 @@
         <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>33</v>
+        <v>74</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>13</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>10</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I2">
+        <v>3400</v>
+      </c>
+      <c r="J2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" t="s">
+        <v>88</v>
+      </c>
+      <c r="L2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s">
+        <v>89</v>
+      </c>
+      <c r="N2" t="s">
+        <v>90</v>
+      </c>
+      <c r="O2" t="s">
+        <v>91</v>
+      </c>
+      <c r="P2" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>93</v>
+      </c>
+      <c r="R2">
+        <v>3000</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>3000</v>
+      </c>
+      <c r="U2" t="s">
+        <v>94</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2" t="s">
+        <v>69</v>
+      </c>
+      <c r="X2" t="s">
+        <v>95</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3" t="s">
+        <v>87</v>
+      </c>
+      <c r="I3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3" t="s">
+        <v>97</v>
+      </c>
+      <c r="L3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" t="s">
+        <v>89</v>
+      </c>
+      <c r="N3" t="s">
+        <v>98</v>
+      </c>
+      <c r="O3" t="s">
+        <v>46</v>
+      </c>
+      <c r="P3" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>93</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3" t="s">
+        <v>99</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3" t="s">
+        <v>22</v>
+      </c>
+      <c r="X3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -869,7 +1575,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -883,40 +1589,81 @@
         <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>46</v>
+        <v>101</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>47</v>
+        <v>102</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>48</v>
+        <v>103</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>49</v>
+        <v>104</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>51</v>
+        <v>106</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>52</v>
+        <v>107</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>53</v>
+        <v>108</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>55</v>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2" t="s">
+        <v>113</v>
+      </c>
+      <c r="G2" t="s">
+        <v>114</v>
+      </c>
+      <c r="H2">
+        <v>24</v>
+      </c>
+      <c r="I2">
+        <v>125</v>
+      </c>
+      <c r="J2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2">
+        <v>3000</v>
       </c>
     </row>
   </sheetData>
@@ -928,7 +1675,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -943,19 +1690,59 @@
         <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>56</v>
+        <v>115</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>57</v>
+        <v>116</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>58</v>
+        <v>117</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>59</v>
+        <v>118</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>60</v>
+        <v>119</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2">
+        <v>100</v>
+      </c>
+      <c r="C2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D2">
+        <v>100</v>
+      </c>
+      <c r="E2">
+        <v>3750</v>
+      </c>
+      <c r="F2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3">
+        <v>100</v>
+      </c>
+      <c r="C3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D3">
+        <v>100</v>
+      </c>
+      <c r="E3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -983,34 +1770,34 @@
         <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>61</v>
+        <v>121</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1022,7 +1809,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -1031,16 +1818,310 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>122</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>63</v>
+        <v>123</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>64</v>
+        <v>124</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>65</v>
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" t="s">
+        <v>131</v>
+      </c>
+      <c r="D4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" t="s">
+        <v>132</v>
+      </c>
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" t="s">
+        <v>133</v>
+      </c>
+      <c r="D6" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>126</v>
+      </c>
+      <c r="B7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" t="s">
+        <v>135</v>
+      </c>
+      <c r="D7" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>126</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
+        <v>137</v>
+      </c>
+      <c r="D8" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>126</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>139</v>
+      </c>
+      <c r="D9" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>126</v>
+      </c>
+      <c r="B10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" t="s">
+        <v>141</v>
+      </c>
+      <c r="D10" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>143</v>
+      </c>
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" t="s">
+        <v>129</v>
+      </c>
+      <c r="D11" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" t="s">
+        <v>145</v>
+      </c>
+      <c r="D12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>146</v>
+      </c>
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" t="s">
+        <v>147</v>
+      </c>
+      <c r="D13" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>96</v>
+      </c>
+      <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" t="s">
+        <v>133</v>
+      </c>
+      <c r="D14" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" t="s">
+        <v>127</v>
+      </c>
+      <c r="D15" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" t="s">
+        <v>127</v>
+      </c>
+      <c r="D16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" t="s">
+        <v>129</v>
+      </c>
+      <c r="D17" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" t="s">
+        <v>145</v>
+      </c>
+      <c r="D18" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" t="s">
+        <v>49</v>
+      </c>
+      <c r="C19" t="s">
+        <v>132</v>
+      </c>
+      <c r="D19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" t="s">
+        <v>133</v>
+      </c>
+      <c r="D20" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21" t="s">
+        <v>137</v>
+      </c>
+      <c r="D21" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>50</v>
+      </c>
+      <c r="B22" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22" t="s">
+        <v>139</v>
+      </c>
+      <c r="D22" t="s">
+        <v>140</v>
       </c>
     </row>
   </sheetData>
